--- a/public/downloads/BOI0044_Confirm Balance 2024.xlsx
+++ b/public/downloads/BOI0044_Confirm Balance 2024.xlsx
@@ -7,9 +7,9 @@
     <workbookView activeTab="1" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="BL.2023(B.1)" sheetId="1" r:id="rId4"/>
-    <sheet name="RTN.2023(B.1)" sheetId="2" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId6"/>
+    <sheet name="BL" sheetId="1" r:id="rId4"/>
+    <sheet name="RTN" sheetId="2" r:id="rId5"/>
+    <sheet name="NGREPORT" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="74">
   <si>
     <t>TOKYO BYOKANE (THAILAND) CO.,LTD.</t>
   </si>
@@ -242,6 +242,21 @@
   </si>
   <si>
     <t>B24-V-N0028858</t>
+  </si>
+  <si>
+    <t>NG REPORT</t>
+  </si>
+  <si>
+    <t>NG Date(Y/M/D)</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Sale QTY</t>
+  </si>
+  <si>
+    <t>2024/3/19</t>
   </si>
 </sst>
 </file>
@@ -842,25 +857,117 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -871,14 +978,27 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -906,17 +1026,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -932,100 +1041,6 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -1538,23 +1553,159 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="31" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="167" fillId="5" borderId="31" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="167" fillId="5" borderId="23" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="167" fillId="5" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="5" borderId="31" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="5" borderId="23" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="5" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="31" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="33" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="34" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="3" borderId="35" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="3" borderId="27" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="3" borderId="31" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="3" borderId="23" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="6" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="6" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="6" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="3" borderId="36" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="3" borderId="37" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="3" borderId="38" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="39" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="35" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="40" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="30" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false"/>
+    </xf>
     <xf xfId="0" fontId="13" numFmtId="0" fillId="7" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="7" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="7" borderId="41" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="7" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="7" borderId="42" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="33" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="34" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="43" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
@@ -1562,47 +1713,43 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="30" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="5" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="14" numFmtId="0" fillId="5" borderId="41" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="5" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="14" numFmtId="0" fillId="5" borderId="42" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="3" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="14" numFmtId="0" fillId="3" borderId="41" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="3" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="14" numFmtId="0" fillId="3" borderId="42" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="4" borderId="35" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="4" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="4" borderId="36" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="4" borderId="45" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="4" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="4" borderId="41" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="4" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="4" borderId="42" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="7" borderId="37" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="7" borderId="39" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="7" borderId="38" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="7" borderId="46" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
@@ -1610,143 +1757,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="39" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="36" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="40" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="41" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="42" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="41" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="41" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="41" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="6" borderId="41" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="6" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="6" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="164" fillId="3" borderId="39" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="164" fillId="3" borderId="43" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="164" fillId="3" borderId="44" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="37" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="45" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="167" fillId="5" borderId="41" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="167" fillId="5" borderId="23" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="167" fillId="5" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="164" fillId="5" borderId="41" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="164" fillId="5" borderId="23" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="164" fillId="5" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="41" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="42" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="46" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
     <xf xfId="0" fontId="1" numFmtId="167" fillId="4" borderId="47" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="3" borderId="34" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="3" borderId="27" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="3" borderId="41" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection hidden="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="167" fillId="3" borderId="23" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection hidden="false"/>
     </xf>
@@ -2160,10 +2175,10 @@
       <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="151" t="s">
+      <c r="C3" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="152"/>
+      <c r="D3" s="185"/>
       <c r="E3" s="88"/>
       <c r="F3" s="29"/>
       <c r="G3" s="29"/>
@@ -2173,15 +2188,15 @@
       <c r="O3" s="13"/>
       <c r="P3" s="14"/>
       <c r="Q3" s="14"/>
-      <c r="T3" s="153"/>
-      <c r="U3" s="153"/>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="153"/>
-      <c r="Y3" s="153"/>
-      <c r="Z3" s="153"/>
-      <c r="AA3" s="153"/>
-      <c r="AB3" s="153"/>
+      <c r="T3" s="186"/>
+      <c r="U3" s="186"/>
+      <c r="V3" s="186"/>
+      <c r="W3" s="186"/>
+      <c r="X3" s="186"/>
+      <c r="Y3" s="186"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="186"/>
+      <c r="AB3" s="186"/>
       <c r="AC3" s="70"/>
       <c r="AG3" s="11"/>
       <c r="AH3" s="10"/>
@@ -2193,15 +2208,15 @@
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="138"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="172"/>
+      <c r="I4" s="173"/>
       <c r="AG4" s="56" t="s">
         <v>7</v>
       </c>
@@ -2214,163 +2229,163 @@
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
       <c r="E5" s="62"/>
-      <c r="F5" s="147" t="s">
+      <c r="F5" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="149"/>
-      <c r="K5" s="149"/>
-      <c r="L5" s="149"/>
-      <c r="M5" s="149"/>
-      <c r="N5" s="149"/>
-      <c r="O5" s="149"/>
-      <c r="P5" s="149"/>
-      <c r="Q5" s="149"/>
-      <c r="R5" s="149"/>
-      <c r="S5" s="149"/>
-      <c r="T5" s="149"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="149"/>
-      <c r="W5" s="149"/>
-      <c r="X5" s="149"/>
-      <c r="Y5" s="149"/>
-      <c r="Z5" s="149"/>
-      <c r="AA5" s="149"/>
-      <c r="AB5" s="149"/>
-      <c r="AC5" s="150"/>
-      <c r="AD5" s="145" t="s">
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="182"/>
+      <c r="K5" s="182"/>
+      <c r="L5" s="182"/>
+      <c r="M5" s="182"/>
+      <c r="N5" s="182"/>
+      <c r="O5" s="182"/>
+      <c r="P5" s="182"/>
+      <c r="Q5" s="182"/>
+      <c r="R5" s="182"/>
+      <c r="S5" s="182"/>
+      <c r="T5" s="182"/>
+      <c r="U5" s="182"/>
+      <c r="V5" s="182"/>
+      <c r="W5" s="182"/>
+      <c r="X5" s="182"/>
+      <c r="Y5" s="182"/>
+      <c r="Z5" s="182"/>
+      <c r="AA5" s="182"/>
+      <c r="AB5" s="182"/>
+      <c r="AC5" s="183"/>
+      <c r="AD5" s="178" t="s">
         <v>9</v>
       </c>
-      <c r="AE5" s="146"/>
-      <c r="AF5" s="143" t="s">
+      <c r="AE5" s="179"/>
+      <c r="AF5" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="AG5" s="144"/>
+      <c r="AG5" s="177"/>
       <c r="AH5" s="10"/>
       <c r="AI5" s="10"/>
       <c r="AJ5" s="10"/>
       <c r="AK5" s="10"/>
     </row>
     <row r="6" spans="1:45" customHeight="1" ht="11.5">
-      <c r="A6" s="158" t="s">
+      <c r="A6" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="161" t="s">
+      <c r="B6" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="164" t="s">
+      <c r="C6" s="158" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="167" t="s">
+      <c r="D6" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="170" t="s">
+      <c r="E6" s="164" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="173" t="s">
+      <c r="F6" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="140"/>
-      <c r="H6" s="139" t="s">
+      <c r="G6" s="168"/>
+      <c r="H6" s="174" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="140"/>
-      <c r="J6" s="154" t="s">
+      <c r="I6" s="168"/>
+      <c r="J6" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="140"/>
-      <c r="L6" s="154" t="s">
+      <c r="K6" s="168"/>
+      <c r="L6" s="187" t="s">
         <v>19</v>
       </c>
-      <c r="M6" s="140"/>
-      <c r="N6" s="154" t="s">
+      <c r="M6" s="168"/>
+      <c r="N6" s="187" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="140"/>
-      <c r="P6" s="156" t="s">
+      <c r="O6" s="168"/>
+      <c r="P6" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="Q6" s="156"/>
-      <c r="R6" s="156" t="s">
+      <c r="Q6" s="136"/>
+      <c r="R6" s="136" t="s">
         <v>22</v>
       </c>
-      <c r="S6" s="156"/>
-      <c r="T6" s="156" t="s">
+      <c r="S6" s="136"/>
+      <c r="T6" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="U6" s="156"/>
-      <c r="V6" s="156" t="s">
+      <c r="U6" s="136"/>
+      <c r="V6" s="136" t="s">
         <v>24</v>
       </c>
-      <c r="W6" s="156"/>
-      <c r="X6" s="156" t="s">
+      <c r="W6" s="136"/>
+      <c r="X6" s="136" t="s">
         <v>25</v>
       </c>
-      <c r="Y6" s="156"/>
-      <c r="Z6" s="181" t="s">
+      <c r="Y6" s="136"/>
+      <c r="Z6" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="AA6" s="181"/>
-      <c r="AB6" s="181" t="s">
+      <c r="AA6" s="144"/>
+      <c r="AB6" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="AC6" s="183"/>
-      <c r="AD6" s="185" t="s">
+      <c r="AC6" s="146"/>
+      <c r="AD6" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="AE6" s="187" t="s">
+      <c r="AE6" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="AF6" s="175" t="s">
+      <c r="AF6" s="138" t="s">
         <v>29</v>
       </c>
-      <c r="AG6" s="178" t="s">
+      <c r="AG6" s="141" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:45" customHeight="1" ht="11.5">
-      <c r="A7" s="159"/>
-      <c r="B7" s="162"/>
-      <c r="C7" s="165"/>
-      <c r="D7" s="168"/>
-      <c r="E7" s="171"/>
-      <c r="F7" s="174"/>
-      <c r="G7" s="142"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="142"/>
-      <c r="J7" s="155"/>
-      <c r="K7" s="142"/>
-      <c r="L7" s="155"/>
-      <c r="M7" s="142"/>
-      <c r="N7" s="155"/>
-      <c r="O7" s="142"/>
-      <c r="P7" s="157"/>
-      <c r="Q7" s="157"/>
-      <c r="R7" s="157"/>
-      <c r="S7" s="157"/>
-      <c r="T7" s="157"/>
-      <c r="U7" s="157"/>
-      <c r="V7" s="157"/>
-      <c r="W7" s="157"/>
-      <c r="X7" s="157"/>
-      <c r="Y7" s="157"/>
-      <c r="Z7" s="182"/>
-      <c r="AA7" s="182"/>
-      <c r="AB7" s="182"/>
-      <c r="AC7" s="184"/>
-      <c r="AD7" s="186"/>
-      <c r="AE7" s="188"/>
-      <c r="AF7" s="176"/>
-      <c r="AG7" s="179"/>
+      <c r="A7" s="153"/>
+      <c r="B7" s="156"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="170"/>
+      <c r="H7" s="175"/>
+      <c r="I7" s="170"/>
+      <c r="J7" s="188"/>
+      <c r="K7" s="170"/>
+      <c r="L7" s="188"/>
+      <c r="M7" s="170"/>
+      <c r="N7" s="188"/>
+      <c r="O7" s="170"/>
+      <c r="P7" s="137"/>
+      <c r="Q7" s="137"/>
+      <c r="R7" s="137"/>
+      <c r="S7" s="137"/>
+      <c r="T7" s="137"/>
+      <c r="U7" s="137"/>
+      <c r="V7" s="137"/>
+      <c r="W7" s="137"/>
+      <c r="X7" s="137"/>
+      <c r="Y7" s="137"/>
+      <c r="Z7" s="145"/>
+      <c r="AA7" s="145"/>
+      <c r="AB7" s="145"/>
+      <c r="AC7" s="147"/>
+      <c r="AD7" s="149"/>
+      <c r="AE7" s="151"/>
+      <c r="AF7" s="139"/>
+      <c r="AG7" s="142"/>
     </row>
     <row r="8" spans="1:45" customHeight="1" ht="12">
-      <c r="A8" s="160"/>
-      <c r="B8" s="163"/>
-      <c r="C8" s="166"/>
-      <c r="D8" s="169"/>
-      <c r="E8" s="172"/>
+      <c r="A8" s="154"/>
+      <c r="B8" s="157"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="163"/>
+      <c r="E8" s="166"/>
       <c r="F8" s="65" t="s">
         <v>31</v>
       </c>
@@ -2449,8 +2464,8 @@
       <c r="AE8" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="AF8" s="177"/>
-      <c r="AG8" s="180"/>
+      <c r="AF8" s="140"/>
+      <c r="AG8" s="143"/>
     </row>
     <row r="9" spans="1:45" customHeight="1" ht="11.5">
       <c r="A9" s="35">
@@ -2471,7 +2486,7 @@
       <c r="H9" s="52"/>
       <c r="I9" s="53"/>
       <c r="J9" s="52">
-        <v>23400</v>
+        <v>23234</v>
       </c>
       <c r="K9" s="53">
         <v>18000</v>
@@ -2496,11 +2511,11 @@
       <c r="AC9" s="53"/>
       <c r="AD9" s="45">
         <f>SUM(F9+H9+J9+L9+N9+P9+R9+T9+V9+X9+Z9+AB9)</f>
-        <v>23400</v>
+        <v>23234</v>
       </c>
       <c r="AE9" s="45">
         <f>E9+AD9</f>
-        <v>23400</v>
+        <v>23234</v>
       </c>
       <c r="AF9" s="46">
         <f>G9+I9+K9+M9+O9+Q9+S9+U9+W9+Y9+AA9+AC9</f>
@@ -2508,7 +2523,7 @@
       </c>
       <c r="AG9" s="47">
         <f>SUM(AE9-AF9)</f>
-        <v>5400</v>
+        <v>5234</v>
       </c>
     </row>
     <row r="10" spans="1:45" customHeight="1" ht="11.5">
@@ -2589,7 +2604,7 @@
       <c r="H11" s="52"/>
       <c r="I11" s="53"/>
       <c r="J11" s="52">
-        <v>11700</v>
+        <v>12000</v>
       </c>
       <c r="K11" s="53">
         <v>12000</v>
@@ -2614,11 +2629,11 @@
       <c r="AC11" s="53"/>
       <c r="AD11" s="45">
         <f>SUM(F11+H11+J11+L11+N11+P11+R11+T11+V11+X11+Z11+AB11)</f>
-        <v>11700</v>
+        <v>12000</v>
       </c>
       <c r="AE11" s="45">
         <f>E11+AD11</f>
-        <v>11700</v>
+        <v>12000</v>
       </c>
       <c r="AF11" s="46">
         <f>G11+I11+K11+M11+O11+Q11+S11+U11+W11+Y11+AA11+AC11</f>
@@ -2626,7 +2641,7 @@
       </c>
       <c r="AG11" s="47">
         <f>SUM(AE11-AF11)</f>
-        <v>-300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:45" customHeight="1" ht="11.5">
@@ -4612,7 +4627,7 @@
       </c>
       <c r="J50" s="19">
         <f>SUM(J9:J49)</f>
-        <v>291100</v>
+        <v>291234</v>
       </c>
       <c r="K50" s="41">
         <f>SUM(K9:K49)</f>
@@ -4692,11 +4707,11 @@
       </c>
       <c r="AD50" s="31">
         <f>SUM(AD9:AD49)</f>
-        <v>291100</v>
+        <v>291234</v>
       </c>
       <c r="AE50" s="32">
         <f>SUM(AE9:AE49)</f>
-        <v>291100</v>
+        <v>291234</v>
       </c>
       <c r="AF50" s="36">
         <f>SUM(AF9:AF49)</f>
@@ -4704,7 +4719,7 @@
       </c>
       <c r="AG50" s="20">
         <f>SUM(AG9:AG49)</f>
-        <v>133816</v>
+        <v>133950</v>
       </c>
     </row>
     <row r="51" spans="1:45" customHeight="1" ht="11.5">
@@ -4806,6 +4821,23 @@
   </sheetData>
   <sheetProtection objects="1" scenarios="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" sort="1" autoFilter="1" pivotTables="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="H6:I7"/>
+    <mergeCell ref="AF5:AG5"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="F5:AC5"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="T3:AB3"/>
+    <mergeCell ref="J6:K7"/>
+    <mergeCell ref="L6:M7"/>
+    <mergeCell ref="N6:O7"/>
+    <mergeCell ref="P6:Q7"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:G7"/>
     <mergeCell ref="R6:S7"/>
     <mergeCell ref="T6:U7"/>
     <mergeCell ref="AF6:AF8"/>
@@ -4816,23 +4848,6 @@
     <mergeCell ref="AB6:AC7"/>
     <mergeCell ref="AD6:AD7"/>
     <mergeCell ref="AE6:AE7"/>
-    <mergeCell ref="P6:Q7"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="H6:I7"/>
-    <mergeCell ref="AF5:AG5"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="F5:AC5"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="T3:AB3"/>
-    <mergeCell ref="J6:K7"/>
-    <mergeCell ref="L6:M7"/>
-    <mergeCell ref="N6:O7"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0" right="0" top="0.59055118110236" bottom="0.39370078740157" header="0.51181102362205" footer="0.51181102362205"/>
@@ -8433,12 +8448,1079 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="12.5" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="19.26953125" customWidth="true" style="0"/>
+    <col min="2" max="2" width="25.1796875" customWidth="true" style="0"/>
+    <col min="3" max="3" width="46.7265625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="21.6328125" customWidth="true" style="0"/>
+    <col min="5" max="5" width="26.6328125" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
-    <row r="28" spans="1:1" customHeight="1" ht="12"/>
+    <row r="1" spans="1:5" customHeight="1" ht="17.5">
+      <c r="A1" s="189" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+    </row>
+    <row r="2" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A2" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="105" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="116" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="116" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A3" s="82" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="106">
+        <v>42920820</v>
+      </c>
+      <c r="D3" s="112">
+        <v>166</v>
+      </c>
+      <c r="E3" s="112">
+        <v>23400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+    </row>
+    <row r="5" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A5" s="82"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+    </row>
+    <row r="6" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A6" s="82"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="112"/>
+    </row>
+    <row r="7" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A7" s="82"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+    </row>
+    <row r="8" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A8" s="82"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+    </row>
+    <row r="9" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A9" s="94"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
+    </row>
+    <row r="10" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A10" s="94"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="107"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="113"/>
+    </row>
+    <row r="11" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A11" s="94"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="113"/>
+    </row>
+    <row r="12" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+    </row>
+    <row r="13" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="113"/>
+    </row>
+    <row r="14" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A15" s="103"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+    </row>
+    <row r="16" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A16" s="103"/>
+      <c r="B16" s="104"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+    </row>
+    <row r="17" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A17" s="97"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="104"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
+    </row>
+    <row r="18" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="113"/>
+    </row>
+    <row r="19" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A19" s="94"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="113"/>
+      <c r="E19" s="113"/>
+    </row>
+    <row r="20" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A20" s="94"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="113"/>
+    </row>
+    <row r="21" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A21" s="94"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+    </row>
+    <row r="22" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A22" s="94"/>
+      <c r="B22" s="95"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="113"/>
+    </row>
+    <row r="23" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A23" s="94"/>
+      <c r="B23" s="95"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+    </row>
+    <row r="24" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A24" s="94"/>
+      <c r="B24" s="95"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="113"/>
+      <c r="E24" s="113"/>
+    </row>
+    <row r="25" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A25" s="94"/>
+      <c r="B25" s="95"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="113"/>
+      <c r="E25" s="113"/>
+    </row>
+    <row r="26" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A26" s="94"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
+    </row>
+    <row r="27" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A27" s="94"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="113"/>
+      <c r="E27" s="113"/>
+    </row>
+    <row r="28" spans="1:5" customHeight="1" ht="12">
+      <c r="A28" s="94"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="113"/>
+    </row>
+    <row r="29" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A29" s="94"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="113"/>
+      <c r="E29" s="113"/>
+    </row>
+    <row r="30" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A30" s="103"/>
+      <c r="B30" s="104"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+    </row>
+    <row r="31" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A31" s="120"/>
+      <c r="B31" s="98"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="114"/>
+      <c r="E31" s="114"/>
+    </row>
+    <row r="32" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A32" s="94"/>
+      <c r="B32" s="95"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="113"/>
+    </row>
+    <row r="33" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A33" s="94"/>
+      <c r="B33" s="95"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="113"/>
+      <c r="E33" s="113"/>
+    </row>
+    <row r="34" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A34" s="94"/>
+      <c r="B34" s="95"/>
+      <c r="C34" s="107"/>
+      <c r="D34" s="113"/>
+      <c r="E34" s="113"/>
+    </row>
+    <row r="35" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A35" s="94"/>
+      <c r="B35" s="95"/>
+      <c r="C35" s="107"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="113"/>
+    </row>
+    <row r="36" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A36" s="103"/>
+      <c r="B36" s="104"/>
+      <c r="C36" s="104"/>
+      <c r="D36" s="114"/>
+      <c r="E36" s="114"/>
+    </row>
+    <row r="37" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A37" s="97"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="104"/>
+      <c r="D37" s="114"/>
+      <c r="E37" s="114"/>
+    </row>
+    <row r="38" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A38" s="94"/>
+      <c r="B38" s="95"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="113"/>
+      <c r="E38" s="113"/>
+    </row>
+    <row r="39" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A39" s="94"/>
+      <c r="B39" s="95"/>
+      <c r="C39" s="107"/>
+      <c r="D39" s="113"/>
+      <c r="E39" s="113"/>
+    </row>
+    <row r="40" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A40" s="94"/>
+      <c r="B40" s="95"/>
+      <c r="C40" s="107"/>
+      <c r="D40" s="113"/>
+      <c r="E40" s="113"/>
+    </row>
+    <row r="41" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A41" s="94"/>
+      <c r="B41" s="95"/>
+      <c r="C41" s="107"/>
+      <c r="D41" s="113"/>
+      <c r="E41" s="113"/>
+    </row>
+    <row r="42" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A42" s="94"/>
+      <c r="B42" s="95"/>
+      <c r="C42" s="107"/>
+      <c r="D42" s="113"/>
+      <c r="E42" s="113"/>
+    </row>
+    <row r="43" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A43" s="94"/>
+      <c r="B43" s="95"/>
+      <c r="C43" s="107"/>
+      <c r="D43" s="113"/>
+      <c r="E43" s="113"/>
+    </row>
+    <row r="44" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A44" s="94"/>
+      <c r="B44" s="95"/>
+      <c r="C44" s="107"/>
+      <c r="D44" s="113"/>
+      <c r="E44" s="113"/>
+    </row>
+    <row r="45" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A45" s="94"/>
+      <c r="B45" s="95"/>
+      <c r="C45" s="107"/>
+      <c r="D45" s="113"/>
+      <c r="E45" s="113"/>
+    </row>
+    <row r="46" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A46" s="94"/>
+      <c r="B46" s="95"/>
+      <c r="C46" s="107"/>
+      <c r="D46" s="113"/>
+      <c r="E46" s="113"/>
+    </row>
+    <row r="47" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A47" s="94"/>
+      <c r="B47" s="95"/>
+      <c r="C47" s="107"/>
+      <c r="D47" s="113"/>
+      <c r="E47" s="113"/>
+    </row>
+    <row r="48" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A48" s="94"/>
+      <c r="B48" s="95"/>
+      <c r="C48" s="107"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="113"/>
+    </row>
+    <row r="49" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A49" s="94"/>
+      <c r="B49" s="95"/>
+      <c r="C49" s="107"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="113"/>
+    </row>
+    <row r="50" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A50" s="94"/>
+      <c r="B50" s="95"/>
+      <c r="C50" s="107"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="113"/>
+    </row>
+    <row r="51" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A51" s="94"/>
+      <c r="B51" s="95"/>
+      <c r="C51" s="107"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="113"/>
+    </row>
+    <row r="52" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A52" s="103"/>
+      <c r="B52" s="104"/>
+      <c r="C52" s="104"/>
+      <c r="D52" s="114"/>
+      <c r="E52" s="114"/>
+    </row>
+    <row r="53" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A53" s="97"/>
+      <c r="B53" s="98"/>
+      <c r="C53" s="104"/>
+      <c r="D53" s="114"/>
+      <c r="E53" s="114"/>
+    </row>
+    <row r="54" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A54" s="94"/>
+      <c r="B54" s="95"/>
+      <c r="C54" s="107"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="113"/>
+    </row>
+    <row r="55" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A55" s="94"/>
+      <c r="B55" s="95"/>
+      <c r="C55" s="107"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="113"/>
+    </row>
+    <row r="56" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A56" s="94"/>
+      <c r="B56" s="95"/>
+      <c r="C56" s="107"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="113"/>
+    </row>
+    <row r="57" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A57" s="94"/>
+      <c r="B57" s="95"/>
+      <c r="C57" s="107"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="113"/>
+    </row>
+    <row r="58" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A58" s="94"/>
+      <c r="B58" s="95"/>
+      <c r="C58" s="107"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="113"/>
+    </row>
+    <row r="59" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A59" s="94"/>
+      <c r="B59" s="95"/>
+      <c r="C59" s="107"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="113"/>
+    </row>
+    <row r="60" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A60" s="94"/>
+      <c r="B60" s="95"/>
+      <c r="C60" s="107"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+    </row>
+    <row r="61" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A61" s="94"/>
+      <c r="B61" s="95"/>
+      <c r="C61" s="107"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="113"/>
+    </row>
+    <row r="62" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A62" s="94"/>
+      <c r="B62" s="95"/>
+      <c r="C62" s="107"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="113"/>
+    </row>
+    <row r="63" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A63" s="94"/>
+      <c r="B63" s="95"/>
+      <c r="C63" s="107"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="113"/>
+    </row>
+    <row r="64" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A64" s="94"/>
+      <c r="B64" s="95"/>
+      <c r="C64" s="107"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="113"/>
+    </row>
+    <row r="65" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A65" s="94"/>
+      <c r="B65" s="95"/>
+      <c r="C65" s="107"/>
+      <c r="D65" s="113"/>
+      <c r="E65" s="113"/>
+    </row>
+    <row r="66" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A66" s="94"/>
+      <c r="B66" s="95"/>
+      <c r="C66" s="107"/>
+      <c r="D66" s="113"/>
+      <c r="E66" s="113"/>
+    </row>
+    <row r="67" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A67" s="103"/>
+      <c r="B67" s="104"/>
+      <c r="C67" s="104"/>
+      <c r="D67" s="114"/>
+      <c r="E67" s="114"/>
+    </row>
+    <row r="68" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A68" s="97"/>
+      <c r="B68" s="98"/>
+      <c r="C68" s="104"/>
+      <c r="D68" s="114"/>
+      <c r="E68" s="114"/>
+    </row>
+    <row r="69" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A69" s="94"/>
+      <c r="B69" s="95"/>
+      <c r="C69" s="107"/>
+      <c r="D69" s="113"/>
+      <c r="E69" s="113"/>
+    </row>
+    <row r="70" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A70" s="94"/>
+      <c r="B70" s="95"/>
+      <c r="C70" s="107"/>
+      <c r="D70" s="113"/>
+      <c r="E70" s="113"/>
+    </row>
+    <row r="71" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A71" s="94"/>
+      <c r="B71" s="95"/>
+      <c r="C71" s="107"/>
+      <c r="D71" s="113"/>
+      <c r="E71" s="113"/>
+    </row>
+    <row r="72" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A72" s="94"/>
+      <c r="B72" s="95"/>
+      <c r="C72" s="107"/>
+      <c r="D72" s="113"/>
+      <c r="E72" s="113"/>
+    </row>
+    <row r="73" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A73" s="94"/>
+      <c r="B73" s="95"/>
+      <c r="C73" s="107"/>
+      <c r="D73" s="113"/>
+      <c r="E73" s="113"/>
+    </row>
+    <row r="74" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A74" s="94"/>
+      <c r="B74" s="95"/>
+      <c r="C74" s="107"/>
+      <c r="D74" s="113"/>
+      <c r="E74" s="113"/>
+    </row>
+    <row r="75" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A75" s="94"/>
+      <c r="B75" s="95"/>
+      <c r="C75" s="107"/>
+      <c r="D75" s="113"/>
+      <c r="E75" s="113"/>
+    </row>
+    <row r="76" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A76" s="94"/>
+      <c r="B76" s="95"/>
+      <c r="C76" s="107"/>
+      <c r="D76" s="113"/>
+      <c r="E76" s="113"/>
+    </row>
+    <row r="77" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A77" s="94"/>
+      <c r="B77" s="95"/>
+      <c r="C77" s="107"/>
+      <c r="D77" s="113"/>
+      <c r="E77" s="113"/>
+    </row>
+    <row r="78" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A78" s="94"/>
+      <c r="B78" s="95"/>
+      <c r="C78" s="107"/>
+      <c r="D78" s="113"/>
+      <c r="E78" s="113"/>
+    </row>
+    <row r="79" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A79" s="94"/>
+      <c r="B79" s="95"/>
+      <c r="C79" s="107"/>
+      <c r="D79" s="113"/>
+      <c r="E79" s="113"/>
+    </row>
+    <row r="80" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A80" s="94"/>
+      <c r="B80" s="95"/>
+      <c r="C80" s="107"/>
+      <c r="D80" s="113"/>
+      <c r="E80" s="113"/>
+    </row>
+    <row r="81" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A81" s="94"/>
+      <c r="B81" s="95"/>
+      <c r="C81" s="107"/>
+      <c r="D81" s="113"/>
+      <c r="E81" s="113"/>
+    </row>
+    <row r="82" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A82" s="103"/>
+      <c r="B82" s="104"/>
+      <c r="C82" s="104"/>
+      <c r="D82" s="114"/>
+      <c r="E82" s="114"/>
+    </row>
+    <row r="83" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A83" s="97"/>
+      <c r="B83" s="98"/>
+      <c r="C83" s="104"/>
+      <c r="D83" s="114"/>
+      <c r="E83" s="114"/>
+    </row>
+    <row r="84" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A84" s="94"/>
+      <c r="B84" s="95"/>
+      <c r="C84" s="107"/>
+      <c r="D84" s="113"/>
+      <c r="E84" s="113"/>
+    </row>
+    <row r="85" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A85" s="94"/>
+      <c r="B85" s="95"/>
+      <c r="C85" s="107"/>
+      <c r="D85" s="113"/>
+      <c r="E85" s="113"/>
+    </row>
+    <row r="86" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A86" s="94"/>
+      <c r="B86" s="95"/>
+      <c r="C86" s="107"/>
+      <c r="D86" s="113"/>
+      <c r="E86" s="113"/>
+    </row>
+    <row r="87" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A87" s="94"/>
+      <c r="B87" s="95"/>
+      <c r="C87" s="107"/>
+      <c r="D87" s="113"/>
+      <c r="E87" s="113"/>
+    </row>
+    <row r="88" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A88" s="94"/>
+      <c r="B88" s="95"/>
+      <c r="C88" s="107"/>
+      <c r="D88" s="113"/>
+      <c r="E88" s="113"/>
+    </row>
+    <row r="89" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A89" s="94"/>
+      <c r="B89" s="95"/>
+      <c r="C89" s="107"/>
+      <c r="D89" s="113"/>
+      <c r="E89" s="113"/>
+    </row>
+    <row r="90" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A90" s="94"/>
+      <c r="B90" s="95"/>
+      <c r="C90" s="107"/>
+      <c r="D90" s="113"/>
+      <c r="E90" s="113"/>
+    </row>
+    <row r="91" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A91" s="94"/>
+      <c r="B91" s="95"/>
+      <c r="C91" s="107"/>
+      <c r="D91" s="113"/>
+      <c r="E91" s="113"/>
+    </row>
+    <row r="92" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A92" s="94"/>
+      <c r="B92" s="95"/>
+      <c r="C92" s="107"/>
+      <c r="D92" s="113"/>
+      <c r="E92" s="113"/>
+    </row>
+    <row r="93" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A93" s="94"/>
+      <c r="B93" s="95"/>
+      <c r="C93" s="107"/>
+      <c r="D93" s="113"/>
+      <c r="E93" s="113"/>
+    </row>
+    <row r="94" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A94" s="94"/>
+      <c r="B94" s="95"/>
+      <c r="C94" s="107"/>
+      <c r="D94" s="113"/>
+      <c r="E94" s="113"/>
+    </row>
+    <row r="95" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A95" s="94"/>
+      <c r="B95" s="95"/>
+      <c r="C95" s="107"/>
+      <c r="D95" s="113"/>
+      <c r="E95" s="113"/>
+    </row>
+    <row r="96" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A96" s="94"/>
+      <c r="B96" s="95"/>
+      <c r="C96" s="107"/>
+      <c r="D96" s="113"/>
+      <c r="E96" s="113"/>
+    </row>
+    <row r="97" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A97" s="94"/>
+      <c r="B97" s="95"/>
+      <c r="C97" s="107"/>
+      <c r="D97" s="113"/>
+      <c r="E97" s="113"/>
+    </row>
+    <row r="98" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A98" s="94"/>
+      <c r="B98" s="95"/>
+      <c r="C98" s="107"/>
+      <c r="D98" s="113"/>
+      <c r="E98" s="113"/>
+    </row>
+    <row r="99" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A99" s="94"/>
+      <c r="B99" s="95"/>
+      <c r="C99" s="107"/>
+      <c r="D99" s="113"/>
+      <c r="E99" s="113"/>
+    </row>
+    <row r="100" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A100" s="94"/>
+      <c r="B100" s="95"/>
+      <c r="C100" s="107"/>
+      <c r="D100" s="113"/>
+      <c r="E100" s="113"/>
+    </row>
+    <row r="101" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A101" s="103"/>
+      <c r="B101" s="104"/>
+      <c r="C101" s="104"/>
+      <c r="D101" s="114"/>
+      <c r="E101" s="114"/>
+    </row>
+    <row r="102" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A102" s="97"/>
+      <c r="B102" s="98"/>
+      <c r="C102" s="104"/>
+      <c r="D102" s="114"/>
+      <c r="E102" s="114"/>
+    </row>
+    <row r="103" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A103" s="94"/>
+      <c r="B103" s="95"/>
+      <c r="C103" s="107"/>
+      <c r="D103" s="113"/>
+      <c r="E103" s="113"/>
+    </row>
+    <row r="104" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A104" s="94"/>
+      <c r="B104" s="95"/>
+      <c r="C104" s="107"/>
+      <c r="D104" s="113"/>
+      <c r="E104" s="113"/>
+    </row>
+    <row r="105" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A105" s="94"/>
+      <c r="B105" s="95"/>
+      <c r="C105" s="107"/>
+      <c r="D105" s="113"/>
+      <c r="E105" s="113"/>
+    </row>
+    <row r="106" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A106" s="94"/>
+      <c r="B106" s="95"/>
+      <c r="C106" s="107"/>
+      <c r="D106" s="113"/>
+      <c r="E106" s="113"/>
+    </row>
+    <row r="107" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A107" s="94"/>
+      <c r="B107" s="95"/>
+      <c r="C107" s="107"/>
+      <c r="D107" s="113"/>
+      <c r="E107" s="113"/>
+    </row>
+    <row r="108" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A108" s="94"/>
+      <c r="B108" s="95"/>
+      <c r="C108" s="107"/>
+      <c r="D108" s="113"/>
+      <c r="E108" s="113"/>
+    </row>
+    <row r="109" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A109" s="94"/>
+      <c r="B109" s="95"/>
+      <c r="C109" s="107"/>
+      <c r="D109" s="113"/>
+      <c r="E109" s="113"/>
+    </row>
+    <row r="110" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A110" s="94"/>
+      <c r="B110" s="95"/>
+      <c r="C110" s="107"/>
+      <c r="D110" s="113"/>
+      <c r="E110" s="113"/>
+    </row>
+    <row r="111" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A111" s="94"/>
+      <c r="B111" s="95"/>
+      <c r="C111" s="107"/>
+      <c r="D111" s="113"/>
+      <c r="E111" s="113"/>
+    </row>
+    <row r="112" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A112" s="94"/>
+      <c r="B112" s="95"/>
+      <c r="C112" s="107"/>
+      <c r="D112" s="113"/>
+      <c r="E112" s="113"/>
+    </row>
+    <row r="113" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A113" s="94"/>
+      <c r="B113" s="95"/>
+      <c r="C113" s="107"/>
+      <c r="D113" s="113"/>
+      <c r="E113" s="113"/>
+    </row>
+    <row r="114" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A114" s="94"/>
+      <c r="B114" s="95"/>
+      <c r="C114" s="107"/>
+      <c r="D114" s="113"/>
+      <c r="E114" s="113"/>
+    </row>
+    <row r="115" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A115" s="94"/>
+      <c r="B115" s="95"/>
+      <c r="C115" s="107"/>
+      <c r="D115" s="113"/>
+      <c r="E115" s="113"/>
+    </row>
+    <row r="116" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A116" s="94"/>
+      <c r="B116" s="95"/>
+      <c r="C116" s="107"/>
+      <c r="D116" s="113"/>
+      <c r="E116" s="113"/>
+    </row>
+    <row r="117" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A117" s="94"/>
+      <c r="B117" s="95"/>
+      <c r="C117" s="107"/>
+      <c r="D117" s="113"/>
+      <c r="E117" s="113"/>
+    </row>
+    <row r="118" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A118" s="94"/>
+      <c r="B118" s="95"/>
+      <c r="C118" s="107"/>
+      <c r="D118" s="113"/>
+      <c r="E118" s="113"/>
+    </row>
+    <row r="119" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A119" s="73"/>
+      <c r="B119" s="79"/>
+      <c r="C119" s="130"/>
+      <c r="D119" s="115"/>
+      <c r="E119" s="115"/>
+    </row>
+    <row r="120" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A120" s="73"/>
+      <c r="B120" s="79"/>
+      <c r="C120" s="130"/>
+      <c r="D120" s="115"/>
+      <c r="E120" s="115"/>
+    </row>
+    <row r="121" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A121" s="73"/>
+      <c r="B121" s="79"/>
+      <c r="C121" s="130"/>
+      <c r="D121" s="115"/>
+      <c r="E121" s="115"/>
+    </row>
+    <row r="122" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A122" s="73"/>
+      <c r="B122" s="79"/>
+      <c r="C122" s="130"/>
+      <c r="D122" s="115"/>
+      <c r="E122" s="115"/>
+    </row>
+    <row r="123" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A123" s="73"/>
+      <c r="B123" s="79"/>
+      <c r="C123" s="130"/>
+      <c r="D123" s="115"/>
+      <c r="E123" s="115"/>
+    </row>
+    <row r="124" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A124" s="73"/>
+      <c r="B124" s="79"/>
+      <c r="C124" s="130"/>
+      <c r="D124" s="115"/>
+      <c r="E124" s="115"/>
+    </row>
+    <row r="125" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A125" s="73"/>
+      <c r="B125" s="79"/>
+      <c r="C125" s="130"/>
+      <c r="D125" s="115"/>
+      <c r="E125" s="115"/>
+    </row>
+    <row r="126" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A126" s="73"/>
+      <c r="B126" s="79"/>
+      <c r="C126" s="130"/>
+      <c r="D126" s="115"/>
+      <c r="E126" s="115"/>
+    </row>
+    <row r="127" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A127" s="73"/>
+      <c r="B127" s="79"/>
+      <c r="C127" s="130"/>
+      <c r="D127" s="115"/>
+      <c r="E127" s="115"/>
+    </row>
+    <row r="128" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A128" s="73"/>
+      <c r="B128" s="79"/>
+      <c r="C128" s="130"/>
+      <c r="D128" s="115"/>
+      <c r="E128" s="115"/>
+    </row>
+    <row r="129" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A129" s="73"/>
+      <c r="B129" s="79"/>
+      <c r="C129" s="130"/>
+      <c r="D129" s="115"/>
+      <c r="E129" s="115"/>
+    </row>
+    <row r="130" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A130" s="73"/>
+      <c r="B130" s="79"/>
+      <c r="C130" s="130"/>
+      <c r="D130" s="115"/>
+      <c r="E130" s="115"/>
+    </row>
+    <row r="131" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A131" s="73"/>
+      <c r="B131" s="79"/>
+      <c r="C131" s="130"/>
+      <c r="D131" s="115"/>
+      <c r="E131" s="115"/>
+    </row>
+    <row r="132" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A132" s="73"/>
+      <c r="B132" s="79"/>
+      <c r="C132" s="130"/>
+      <c r="D132" s="115"/>
+      <c r="E132" s="115"/>
+    </row>
+    <row r="133" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A133" s="73"/>
+      <c r="B133" s="79"/>
+      <c r="C133" s="130"/>
+      <c r="D133" s="115"/>
+      <c r="E133" s="115"/>
+    </row>
+    <row r="134" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A134" s="73"/>
+      <c r="B134" s="79"/>
+      <c r="C134" s="130"/>
+      <c r="D134" s="115"/>
+      <c r="E134" s="115"/>
+    </row>
+    <row r="135" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A135" s="73"/>
+      <c r="B135" s="79"/>
+      <c r="C135" s="130"/>
+      <c r="D135" s="115"/>
+      <c r="E135" s="115"/>
+    </row>
+    <row r="136" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A136" s="73"/>
+      <c r="B136" s="79"/>
+      <c r="C136" s="130"/>
+      <c r="D136" s="115"/>
+      <c r="E136" s="115"/>
+    </row>
+    <row r="137" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A137" s="73"/>
+      <c r="B137" s="79"/>
+      <c r="C137" s="130"/>
+      <c r="D137" s="115"/>
+      <c r="E137" s="115"/>
+    </row>
+    <row r="138" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A138" s="73"/>
+      <c r="B138" s="79"/>
+      <c r="C138" s="130"/>
+      <c r="D138" s="115"/>
+      <c r="E138" s="115"/>
+    </row>
+    <row r="139" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A139" s="73"/>
+      <c r="B139" s="79"/>
+      <c r="C139" s="130"/>
+      <c r="D139" s="115"/>
+      <c r="E139" s="115"/>
+    </row>
+    <row r="140" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A140" s="73"/>
+      <c r="B140" s="79"/>
+      <c r="C140" s="130"/>
+      <c r="D140" s="115"/>
+      <c r="E140" s="115"/>
+    </row>
+    <row r="141" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A141" s="73"/>
+      <c r="B141" s="79"/>
+      <c r="C141" s="130"/>
+      <c r="D141" s="115"/>
+      <c r="E141" s="115"/>
+    </row>
+    <row r="142" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A142" s="73"/>
+      <c r="B142" s="79"/>
+      <c r="C142" s="130"/>
+      <c r="D142" s="115"/>
+      <c r="E142" s="115"/>
+    </row>
+    <row r="143" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A143" s="73"/>
+      <c r="B143" s="79"/>
+      <c r="C143" s="130"/>
+      <c r="D143" s="115"/>
+      <c r="E143" s="115"/>
+    </row>
+    <row r="144" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A144" s="73"/>
+      <c r="B144" s="79"/>
+      <c r="C144" s="130"/>
+      <c r="D144" s="115"/>
+      <c r="E144" s="115"/>
+    </row>
+    <row r="145" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A145" s="73"/>
+      <c r="B145" s="79"/>
+      <c r="C145" s="130"/>
+      <c r="D145" s="115"/>
+      <c r="E145" s="115"/>
+    </row>
+    <row r="146" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A146" s="73"/>
+      <c r="B146" s="79"/>
+      <c r="C146" s="130"/>
+      <c r="D146" s="115"/>
+      <c r="E146" s="115"/>
+    </row>
+    <row r="147" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A147" s="73"/>
+      <c r="B147" s="79"/>
+      <c r="C147" s="130"/>
+      <c r="D147" s="115"/>
+      <c r="E147" s="115"/>
+    </row>
+    <row r="148" spans="1:5" customHeight="1" ht="12.5">
+      <c r="A148" s="23"/>
+      <c r="B148" s="80"/>
+      <c r="C148" s="131"/>
+      <c r="D148" s="109"/>
+      <c r="E148" s="109"/>
+    </row>
   </sheetData>
   <sheetProtection objects="1" scenarios="1" formatCells="1" formatColumns="1" formatRows="1" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" sort="1" autoFilter="1" pivotTables="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <mergeCells>
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
